--- a/outputs/analysis/analysis_output/tables/part2/missingness_by_cao.xlsx
+++ b/outputs/analysis/analysis_output/tables/part2/missingness_by_cao.xlsx
@@ -634,7 +634,7 @@
         <v>10</v>
       </c>
       <c r="B2" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>96.875</v>
+        <v>78.125</v>
       </c>
     </row>
     <row r="3">
@@ -686,10 +686,10 @@
         <v>21</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>7.142857142857142</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -704,7 +704,7 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>92.85714285714286</v>
       </c>
     </row>
     <row r="5">
@@ -730,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>88.23529411764706</v>
       </c>
     </row>
     <row r="6">
@@ -750,13 +750,13 @@
         <v>5.555555555555555</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>94.44444444444444</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -764,7 +764,7 @@
         <v>41</v>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -782,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -808,7 +808,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -816,7 +816,7 @@
         <v>50</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>75</v>
+        <v>91.66666666666666</v>
       </c>
     </row>
     <row r="10">
@@ -842,7 +842,7 @@
         <v>51</v>
       </c>
       <c r="B10" t="n">
-        <v>42.85714285714285</v>
+        <v>9.523809523809524</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -868,7 +868,7 @@
         <v>80</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -886,7 +886,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>100</v>
+        <v>92.30769230769231</v>
       </c>
     </row>
     <row r="12">
@@ -894,7 +894,7 @@
         <v>83</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>7.142857142857142</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -938,7 +938,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>53.33333333333334</v>
+        <v>26.66666666666667</v>
       </c>
     </row>
     <row r="14">
@@ -946,7 +946,7 @@
         <v>156</v>
       </c>
       <c r="B14" t="n">
-        <v>55.55555555555556</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -972,7 +972,7 @@
         <v>157</v>
       </c>
       <c r="B15" t="n">
-        <v>17.64705882352941</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -984,13 +984,13 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="H15" t="n">
-        <v>94.11764705882352</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -998,25 +998,25 @@
         <v>163</v>
       </c>
       <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9.090909090909092</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
         <v>90.90909090909091</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>9.090909090909092</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -1027,7 +1027,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1050,7 +1050,7 @@
         <v>214</v>
       </c>
       <c r="B18" t="n">
-        <v>28.57142857142857</v>
+        <v>9.523809523809524</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>218</v>
       </c>
       <c r="B19" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -1091,10 +1091,10 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>83.33333333333334</v>
       </c>
     </row>
     <row r="20">
@@ -1114,13 +1114,13 @@
         <v>5.88235294117647</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="G20" t="n">
         <v>5.88235294117647</v>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>94.11764705882352</v>
       </c>
     </row>
     <row r="21">
@@ -1128,7 +1128,7 @@
         <v>234</v>
       </c>
       <c r="B21" t="n">
-        <v>90</v>
+        <v>5</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -1154,7 +1154,7 @@
         <v>243</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>3.846153846153846</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -1166,13 +1166,13 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>3.846153846153846</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>3.846153846153846</v>
       </c>
       <c r="H22" t="n">
-        <v>84.61538461538461</v>
+        <v>88.46153846153845</v>
       </c>
     </row>
     <row r="23">
@@ -1198,7 +1198,7 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>64.28571428571429</v>
+        <v>50</v>
       </c>
     </row>
     <row r="24">
@@ -1206,7 +1206,7 @@
         <v>254</v>
       </c>
       <c r="B24" t="n">
-        <v>19.04761904761905</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -1232,7 +1232,7 @@
         <v>301</v>
       </c>
       <c r="B25" t="n">
-        <v>46.15384615384615</v>
+        <v>3.846153846153846</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
@@ -1244,10 +1244,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>3.846153846153846</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>3.846153846153846</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>306</v>
       </c>
       <c r="B26" t="n">
-        <v>42.85714285714285</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>100</v>
+        <v>85.71428571428571</v>
       </c>
     </row>
     <row r="27">
@@ -1310,7 +1310,7 @@
         <v>317</v>
       </c>
       <c r="B28" t="n">
-        <v>7.142857142857142</v>
+        <v>30.76923076923077</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1325,10 +1325,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="H28" t="n">
-        <v>100</v>
+        <v>15.38461538461539</v>
       </c>
     </row>
     <row r="29">
@@ -1336,7 +1336,7 @@
         <v>331</v>
       </c>
       <c r="B29" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
@@ -1406,7 +1406,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>100</v>
+        <v>91.66666666666666</v>
       </c>
     </row>
     <row r="32">
@@ -1414,7 +1414,7 @@
         <v>433</v>
       </c>
       <c r="B32" t="n">
-        <v>21.42857142857143</v>
+        <v>3.571428571428571</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -1475,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1510,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>43.75</v>
+        <v>68.75</v>
       </c>
     </row>
     <row r="36">
@@ -1518,25 +1518,25 @@
         <v>496</v>
       </c>
       <c r="B36" t="n">
-        <v>72</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="37">
@@ -1596,7 +1596,7 @@
         <v>526</v>
       </c>
       <c r="B39" t="n">
-        <v>55.55555555555556</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
@@ -1651,22 +1651,22 @@
         <v>7.692307692307693</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>7.692307692307693</v>
       </c>
       <c r="H41" t="n">
-        <v>100</v>
+        <v>92.30769230769231</v>
       </c>
     </row>
     <row r="42">
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>100</v>
+        <v>94.44444444444444</v>
       </c>
     </row>
     <row r="44">
@@ -1744,7 +1744,7 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>100</v>
+        <v>78.57142857142857</v>
       </c>
     </row>
     <row r="45">
@@ -1770,7 +1770,7 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1830,7 +1830,7 @@
         <v>625</v>
       </c>
       <c r="B48" t="n">
-        <v>90.90909090909091</v>
+        <v>0</v>
       </c>
       <c r="C48" t="n">
         <v>0</v>
@@ -1874,7 +1874,7 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50">
@@ -1888,7 +1888,7 @@
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>15.38461538461539</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -1900,7 +1900,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>82.05128205128204</v>
+        <v>56.41025641025641</v>
       </c>
     </row>
     <row r="51">
@@ -1908,7 +1908,7 @@
         <v>637</v>
       </c>
       <c r="B51" t="n">
-        <v>11.76470588235294</v>
+        <v>0</v>
       </c>
       <c r="C51" t="n">
         <v>0</v>
@@ -1946,13 +1946,13 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="H52" t="n">
-        <v>100</v>
+        <v>95.23809523809523</v>
       </c>
     </row>
     <row r="53">
@@ -1960,16 +1960,16 @@
         <v>679</v>
       </c>
       <c r="B53" t="n">
-        <v>3.571428571428571</v>
+        <v>0</v>
       </c>
       <c r="C53" t="n">
-        <v>17.85714285714286</v>
+        <v>0</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
       </c>
       <c r="E53" t="n">
-        <v>3.571428571428571</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>89.28571428571429</v>
+        <v>85.71428571428571</v>
       </c>
     </row>
     <row r="54">
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="H54" t="n">
         <v>100</v>
@@ -2012,7 +2012,7 @@
         <v>721</v>
       </c>
       <c r="B55" t="n">
-        <v>77.77777777777779</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="H55" t="n">
-        <v>66.66666666666666</v>
+        <v>22.22222222222222</v>
       </c>
     </row>
     <row r="56">
@@ -2038,25 +2038,25 @@
         <v>725</v>
       </c>
       <c r="B56" t="n">
-        <v>0</v>
+        <v>4.347826086956522</v>
       </c>
       <c r="C56" t="n">
-        <v>4.347826086956522</v>
+        <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>4.347826086956522</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
-        <v>4.347826086956522</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
         <v>4.347826086956522</v>
       </c>
       <c r="G56" t="n">
-        <v>4.347826086956522</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>95.65217391304348</v>
+        <v>47.82608695652174</v>
       </c>
     </row>
     <row r="57">
@@ -2064,7 +2064,7 @@
         <v>727</v>
       </c>
       <c r="B57" t="n">
-        <v>0</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="C57" t="n">
         <v>0</v>
@@ -2076,10 +2076,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>2.777777777777778</v>
       </c>
       <c r="H57" t="n">
         <v>69.44444444444444</v>
@@ -2090,10 +2090,10 @@
         <v>730</v>
       </c>
       <c r="B58" t="n">
-        <v>23.52941176470588</v>
+        <v>11.76470588235294</v>
       </c>
       <c r="C58" t="n">
-        <v>0</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>748</v>
       </c>
       <c r="B59" t="n">
-        <v>82.35294117647058</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="C59" t="n">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>750</v>
       </c>
       <c r="B60" t="n">
-        <v>92.30769230769231</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>91.66666666666666</v>
       </c>
     </row>
     <row r="61">
@@ -2168,7 +2168,7 @@
         <v>759</v>
       </c>
       <c r="B61" t="n">
-        <v>0</v>
+        <v>4.166666666666666</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
@@ -2186,7 +2186,7 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>100</v>
+        <v>95.83333333333334</v>
       </c>
     </row>
     <row r="62">
@@ -2220,16 +2220,16 @@
         <v>822</v>
       </c>
       <c r="B63" t="n">
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="C63" t="n">
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>6.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
@@ -2238,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>86.66666666666667</v>
+        <v>85.71428571428571</v>
       </c>
     </row>
     <row r="64">
@@ -2258,10 +2258,10 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="H64" t="n">
         <v>100</v>
@@ -2298,16 +2298,16 @@
         <v>826</v>
       </c>
       <c r="B66" t="n">
-        <v>5.88235294117647</v>
+        <v>0</v>
       </c>
       <c r="C66" t="n">
-        <v>11.76470588235294</v>
+        <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>11.76470588235294</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
-        <v>11.76470588235294</v>
+        <v>0</v>
       </c>
       <c r="F66" t="n">
         <v>0</v>
@@ -2316,7 +2316,7 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>82.35294117647058</v>
+        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="67">
@@ -2342,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>50</v>
+        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="68">
@@ -2365,7 +2365,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>15.38461538461539</v>
       </c>
       <c r="H68" t="n">
         <v>76.92307692307693</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>41.17647058823529</v>
+        <v>64.70588235294117</v>
       </c>
     </row>
     <row r="70">
@@ -2428,7 +2428,7 @@
         <v>1022</v>
       </c>
       <c r="B71" t="n">
-        <v>53.33333333333334</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="C71" t="n">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>66.66666666666666</v>
+        <v>72.72727272727273</v>
       </c>
     </row>
     <row r="72">
@@ -2454,25 +2454,25 @@
         <v>1060</v>
       </c>
       <c r="B72" t="n">
-        <v>60</v>
+        <v>61.90476190476191</v>
       </c>
       <c r="C72" t="n">
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>4.761904761904762</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>76</v>
+        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="73">
@@ -2480,25 +2480,25 @@
         <v>1165</v>
       </c>
       <c r="B73" t="n">
-        <v>21.42857142857143</v>
+        <v>8</v>
       </c>
       <c r="C73" t="n">
-        <v>7.142857142857142</v>
+        <v>8</v>
       </c>
       <c r="D73" t="n">
-        <v>7.142857142857142</v>
+        <v>8</v>
       </c>
       <c r="E73" t="n">
-        <v>7.142857142857142</v>
+        <v>8</v>
       </c>
       <c r="F73" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G73" t="n">
-        <v>3.571428571428571</v>
+        <v>8</v>
       </c>
       <c r="H73" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74">
@@ -2506,7 +2506,7 @@
         <v>1188</v>
       </c>
       <c r="B74" t="n">
-        <v>44.44444444444444</v>
+        <v>12.5</v>
       </c>
       <c r="C74" t="n">
         <v>0</v>
@@ -2558,25 +2558,25 @@
         <v>1287</v>
       </c>
       <c r="B76" t="n">
-        <v>5.555555555555555</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="C76" t="n">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="E76" t="n">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="F76" t="n">
-        <v>0</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="H76" t="n">
-        <v>44.44444444444444</v>
+        <v>53.33333333333334</v>
       </c>
     </row>
     <row r="77">
@@ -2587,19 +2587,19 @@
         <v>100</v>
       </c>
       <c r="C77" t="n">
-        <v>14.28571428571428</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="D77" t="n">
-        <v>14.28571428571428</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="G77" t="n">
-        <v>14.28571428571428</v>
+        <v>16.66666666666666</v>
       </c>
       <c r="H77" t="n">
         <v>100</v>
@@ -2610,7 +2610,7 @@
         <v>1296</v>
       </c>
       <c r="B78" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C78" t="n">
         <v>0</v>
@@ -2636,7 +2636,7 @@
         <v>1345</v>
       </c>
       <c r="B79" t="n">
-        <v>57.14285714285714</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="C79" t="n">
         <v>0</v>
@@ -2654,7 +2654,7 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>100</v>
+        <v>66.66666666666666</v>
       </c>
     </row>
     <row r="80">
@@ -2688,7 +2688,7 @@
         <v>1471</v>
       </c>
       <c r="B81" t="n">
-        <v>16.66666666666666</v>
+        <v>0</v>
       </c>
       <c r="C81" t="n">
         <v>0</v>
@@ -2714,25 +2714,25 @@
         <v>1494</v>
       </c>
       <c r="B82" t="n">
-        <v>72.22222222222221</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="C82" t="n">
-        <v>5.555555555555555</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="D82" t="n">
-        <v>5.555555555555555</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="E82" t="n">
-        <v>5.555555555555555</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="F82" t="n">
-        <v>5.555555555555555</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="H82" t="n">
-        <v>100</v>
+        <v>93.33333333333333</v>
       </c>
     </row>
     <row r="83">
@@ -2740,7 +2740,7 @@
         <v>1496</v>
       </c>
       <c r="B83" t="n">
-        <v>22.22222222222222</v>
+        <v>10</v>
       </c>
       <c r="C83" t="n">
         <v>0</v>
@@ -2758,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>44.44444444444444</v>
+        <v>85</v>
       </c>
     </row>
     <row r="84">
@@ -2792,7 +2792,7 @@
         <v>1536</v>
       </c>
       <c r="B85" t="n">
-        <v>76.92307692307693</v>
+        <v>0</v>
       </c>
       <c r="C85" t="n">
         <v>0</v>
@@ -2810,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>61.53846153846154</v>
+        <v>36.36363636363637</v>
       </c>
     </row>
     <row r="86">
@@ -2818,7 +2818,7 @@
         <v>1547</v>
       </c>
       <c r="B86" t="n">
-        <v>0</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="C86" t="n">
         <v>0</v>
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>100</v>
+        <v>88.88888888888889</v>
       </c>
     </row>
     <row r="87">
@@ -2844,7 +2844,7 @@
         <v>1574</v>
       </c>
       <c r="B87" t="n">
-        <v>18.18181818181818</v>
+        <v>22.22222222222222</v>
       </c>
       <c r="C87" t="n">
         <v>0</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>81.81818181818183</v>
+        <v>77.77777777777779</v>
       </c>
     </row>
     <row r="88">
@@ -2870,7 +2870,7 @@
         <v>1612</v>
       </c>
       <c r="B88" t="n">
-        <v>38.09523809523809</v>
+        <v>0</v>
       </c>
       <c r="C88" t="n">
         <v>0</v>
@@ -2896,25 +2896,25 @@
         <v>1618</v>
       </c>
       <c r="B89" t="n">
-        <v>90</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="C89" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="E89" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="H89" t="n">
-        <v>60</v>
+        <v>57.14285714285714</v>
       </c>
     </row>
     <row r="90">
@@ -2940,7 +2940,7 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>100</v>
+        <v>90.90909090909091</v>
       </c>
     </row>
     <row r="91">
@@ -2948,7 +2948,7 @@
         <v>1869</v>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
@@ -2966,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>100</v>
+        <v>81.25</v>
       </c>
     </row>
     <row r="92">
@@ -2974,7 +2974,7 @@
         <v>1944</v>
       </c>
       <c r="B92" t="n">
-        <v>34.48275862068966</v>
+        <v>8.333333333333332</v>
       </c>
       <c r="C92" t="n">
         <v>0</v>
@@ -2992,7 +2992,7 @@
         <v>0</v>
       </c>
       <c r="H92" t="n">
-        <v>89.65517241379311</v>
+        <v>79.16666666666666</v>
       </c>
     </row>
     <row r="93">
@@ -3026,7 +3026,7 @@
         <v>2070</v>
       </c>
       <c r="B94" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="C94" t="n">
         <v>0</v>
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>12.5</v>
+        <v>14.28571428571428</v>
       </c>
     </row>
     <row r="95">
@@ -3052,10 +3052,10 @@
         <v>2266</v>
       </c>
       <c r="B95" t="n">
-        <v>7.692307692307693</v>
+        <v>10</v>
       </c>
       <c r="C95" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D95" t="n">
         <v>0</v>
@@ -3070,7 +3070,7 @@
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="96">
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="97">
@@ -3104,7 +3104,7 @@
         <v>2535</v>
       </c>
       <c r="B97" t="n">
-        <v>80.95238095238095</v>
+        <v>5.88235294117647</v>
       </c>
       <c r="C97" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
         <v>0</v>
       </c>
       <c r="H97" t="n">
-        <v>4.761904761904762</v>
+        <v>64.70588235294117</v>
       </c>
     </row>
     <row r="98">
@@ -3130,25 +3130,25 @@
         <v>2948</v>
       </c>
       <c r="B98" t="n">
-        <v>2.702702702702703</v>
+        <v>10.3448275862069</v>
       </c>
       <c r="C98" t="n">
-        <v>0</v>
+        <v>3.448275862068965</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>3.448275862068965</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>3.448275862068965</v>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>3.448275862068965</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>3.448275862068965</v>
       </c>
       <c r="H98" t="n">
-        <v>70.27027027027027</v>
+        <v>51.72413793103448</v>
       </c>
     </row>
     <row r="99">
@@ -3156,7 +3156,7 @@
         <v>3313</v>
       </c>
       <c r="B99" t="n">
-        <v>78.57142857142857</v>
+        <v>92.30769230769231</v>
       </c>
       <c r="C99" t="n">
         <v>0</v>
@@ -3174,7 +3174,7 @@
         <v>0</v>
       </c>
       <c r="H99" t="n">
-        <v>7.142857142857142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -3182,7 +3182,7 @@
         <v>3335</v>
       </c>
       <c r="B100" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
         <v>0</v>
